--- a/data/trans_orig/P2A_enfcro_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2A_enfcro_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17944</t>
+          <t>18426</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31681</t>
+          <t>31077</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18524</t>
+          <t>18222</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31732</t>
+          <t>30892</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39722</t>
+          <t>39874</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58595</t>
+          <t>58280</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,32%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48774</t>
+          <t>49378</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62511</t>
+          <t>62029</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39905</t>
+          <t>40745</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53113</t>
+          <t>53415</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>93497</t>
+          <t>93812</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112370</t>
+          <t>112218</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,78%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23546</t>
+          <t>23928</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37270</t>
+          <t>37296</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25714</t>
+          <t>24865</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38306</t>
+          <t>38570</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52085</t>
+          <t>51806</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71328</t>
+          <t>70362</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>51,67%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31417</t>
+          <t>31391</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45141</t>
+          <t>44759</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29179</t>
+          <t>28915</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41771</t>
+          <t>42620</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>64844</t>
+          <t>65810</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>84087</t>
+          <t>84366</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,96%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12202</t>
+          <t>12008</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23806</t>
+          <t>23621</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22449</t>
+          <t>22225</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35204</t>
+          <t>35124</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37259</t>
+          <t>37916</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54928</t>
+          <t>55754</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>39,21%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34439</t>
+          <t>34624</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46043</t>
+          <t>46237</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48740</t>
+          <t>48820</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61495</t>
+          <t>61719</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>87261</t>
+          <t>86435</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>104930</t>
+          <t>104273</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,33%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51250</t>
+          <t>51154</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71559</t>
+          <t>71098</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52923</t>
+          <t>52174</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71969</t>
+          <t>73145</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110183</t>
+          <t>109613</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>136697</t>
+          <t>136922</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,66%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>79737</t>
+          <t>80198</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100046</t>
+          <t>100142</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76593</t>
+          <t>75417</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>95639</t>
+          <t>96388</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>163161</t>
+          <t>162936</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>189675</t>
+          <t>190245</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,45%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23921</t>
+          <t>24048</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37407</t>
+          <t>37085</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32561</t>
+          <t>32301</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46821</t>
+          <t>47328</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60580</t>
+          <t>59933</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80259</t>
+          <t>79835</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>51,96%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31716</t>
+          <t>32038</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45202</t>
+          <t>45075</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37709</t>
+          <t>37202</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51969</t>
+          <t>52229</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>73393</t>
+          <t>73817</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>93072</t>
+          <t>93719</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,99%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29535</t>
+          <t>29824</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44070</t>
+          <t>44352</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31561</t>
+          <t>32563</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45782</t>
+          <t>45433</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>66788</t>
+          <t>66196</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>86786</t>
+          <t>86558</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,78%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30800</t>
+          <t>30518</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45335</t>
+          <t>45046</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26610</t>
+          <t>26959</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40831</t>
+          <t>39829</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>60476</t>
+          <t>60704</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>80474</t>
+          <t>81066</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>55,05%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>180297</t>
+          <t>180505</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>216629</t>
+          <t>217675</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>208567</t>
+          <t>208778</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>243856</t>
+          <t>245146</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>402775</t>
+          <t>400611</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>451833</t>
+          <t>453544</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,98%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>286046</t>
+          <t>285000</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>322378</t>
+          <t>322170</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>284693</t>
+          <t>283403</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>319982</t>
+          <t>319771</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>579392</t>
+          <t>577681</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>628450</t>
+          <t>630614</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>61,15%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20047</t>
+          <t>19955</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32156</t>
+          <t>32695</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18951</t>
+          <t>18804</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32326</t>
+          <t>32444</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41245</t>
+          <t>41473</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59568</t>
+          <t>60719</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>45,1%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29065</t>
+          <t>28526</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41174</t>
+          <t>41266</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41084</t>
+          <t>40966</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54459</t>
+          <t>54606</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>75063</t>
+          <t>73912</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>93386</t>
+          <t>93158</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,2%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21607</t>
+          <t>21202</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34597</t>
+          <t>34503</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24510</t>
+          <t>23790</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37845</t>
+          <t>36978</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49516</t>
+          <t>49411</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68623</t>
+          <t>69386</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,82%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30782</t>
+          <t>30876</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43772</t>
+          <t>44177</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30681</t>
+          <t>31548</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44016</t>
+          <t>44736</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65282</t>
+          <t>64519</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>84389</t>
+          <t>84494</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>63,1%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24651</t>
+          <t>24736</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37815</t>
+          <t>38111</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21182</t>
+          <t>21537</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34611</t>
+          <t>34476</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49620</t>
+          <t>49807</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68383</t>
+          <t>68971</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>51,28%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28708</t>
+          <t>28412</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41872</t>
+          <t>41787</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33353</t>
+          <t>33488</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46782</t>
+          <t>46427</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66104</t>
+          <t>65516</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>84867</t>
+          <t>84680</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>62,97%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58030</t>
+          <t>56316</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75487</t>
+          <t>75847</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74989</t>
+          <t>74707</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95423</t>
+          <t>96606</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>138746</t>
+          <t>139328</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>166619</t>
+          <t>167035</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>56,08%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60993</t>
+          <t>60633</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>78450</t>
+          <t>80164</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65941</t>
+          <t>64758</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86375</t>
+          <t>86657</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>131225</t>
+          <t>130809</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>159098</t>
+          <t>158516</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,22%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33276</t>
+          <t>33206</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49878</t>
+          <t>49125</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45459</t>
+          <t>44412</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61154</t>
+          <t>60212</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81670</t>
+          <t>82653</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>104661</t>
+          <t>104345</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,26%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43573</t>
+          <t>44326</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60175</t>
+          <t>60245</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30854</t>
+          <t>31796</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46549</t>
+          <t>47596</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>80798</t>
+          <t>81114</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>103789</t>
+          <t>102806</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,43%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22346</t>
+          <t>22629</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34598</t>
+          <t>34982</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29955</t>
+          <t>29466</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43796</t>
+          <t>44009</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>55287</t>
+          <t>56331</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>74853</t>
+          <t>73932</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>57,78%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19313</t>
+          <t>18929</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31565</t>
+          <t>31282</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30242</t>
+          <t>30029</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44083</t>
+          <t>44572</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>53096</t>
+          <t>54017</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>72662</t>
+          <t>71618</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>55,97%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>205564</t>
+          <t>204644</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>239769</t>
+          <t>239956</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>238277</t>
+          <t>237805</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>276695</t>
+          <t>277451</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>454125</t>
+          <t>455793</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>506605</t>
+          <t>507891</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>50,07%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>237196</t>
+          <t>237009</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>271401</t>
+          <t>272321</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>260615</t>
+          <t>259859</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>299033</t>
+          <t>299505</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>507670</t>
+          <t>506384</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>560150</t>
+          <t>558482</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,06%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20177</t>
+          <t>19824</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33090</t>
+          <t>33172</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23898</t>
+          <t>23588</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37966</t>
+          <t>38171</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47875</t>
+          <t>48245</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67726</t>
+          <t>66963</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>46,8%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31741</t>
+          <t>31659</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44654</t>
+          <t>45007</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40288</t>
+          <t>40083</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54356</t>
+          <t>54666</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>75359</t>
+          <t>76122</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>95210</t>
+          <t>94840</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>66,28%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21648</t>
+          <t>22319</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35947</t>
+          <t>35917</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30432</t>
+          <t>31014</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46089</t>
+          <t>46248</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57833</t>
+          <t>56341</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77563</t>
+          <t>77182</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,01%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46364</t>
+          <t>46394</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>60663</t>
+          <t>59992</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>46978</t>
+          <t>46819</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>62635</t>
+          <t>62053</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>97815</t>
+          <t>98196</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>117545</t>
+          <t>119037</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,87%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13290</t>
+          <t>13643</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24137</t>
+          <t>23941</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17257</t>
+          <t>17236</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29153</t>
+          <t>29127</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33909</t>
+          <t>33274</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50302</t>
+          <t>50042</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,4%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25087</t>
+          <t>25283</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35934</t>
+          <t>35581</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31858</t>
+          <t>31884</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43754</t>
+          <t>43775</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59932</t>
+          <t>60192</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>76325</t>
+          <t>76960</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,81%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64691</t>
+          <t>65099</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85718</t>
+          <t>85824</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50373</t>
+          <t>50390</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70506</t>
+          <t>70016</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120581</t>
+          <t>119458</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>149525</t>
+          <t>148335</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,06%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>80079</t>
+          <t>79973</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101106</t>
+          <t>100698</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>100377</t>
+          <t>100867</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>120510</t>
+          <t>120493</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>187155</t>
+          <t>188345</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>216099</t>
+          <t>217222</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>64,52%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39094</t>
+          <t>39245</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55231</t>
+          <t>55668</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45418</t>
+          <t>45540</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61001</t>
+          <t>62242</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>88041</t>
+          <t>87953</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>111175</t>
+          <t>110765</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,18%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46348</t>
+          <t>45911</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62485</t>
+          <t>62334</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38152</t>
+          <t>36911</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53735</t>
+          <t>53613</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>89557</t>
+          <t>89967</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>112691</t>
+          <t>112779</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>56,18%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20811</t>
+          <t>20553</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33206</t>
+          <t>33842</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21662</t>
+          <t>21654</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35072</t>
+          <t>35345</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46271</t>
+          <t>46769</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>63602</t>
+          <t>65105</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>50,8%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>26492</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39523</t>
+          <t>39781</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32753</t>
+          <t>32480</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46163</t>
+          <t>46171</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>64557</t>
+          <t>63054</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>81888</t>
+          <t>81390</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>63,51%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>204592</t>
+          <t>203032</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>240017</t>
+          <t>240353</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>215072</t>
+          <t>212206</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>252716</t>
+          <t>251055</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>430010</t>
+          <t>429128</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>484228</t>
+          <t>480035</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>43,87%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>284059</t>
+          <t>283723</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>319484</t>
+          <t>321044</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>317476</t>
+          <t>319137</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>355120</t>
+          <t>357986</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>610040</t>
+          <t>614233</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>664258</t>
+          <t>665140</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>60,78%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>99028</t>
+          <t>98746</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>103920</t>
+          <t>103938</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>131170</t>
+          <t>130363</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>136291</t>
+          <t>136254</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>232628</t>
+          <t>233419</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>239502</t>
+          <t>239627</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>524</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>6545</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8742</t>
+          <t>7951</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87951</t>
+          <t>87828</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93930</t>
+          <t>93933</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -9016,7 +9016,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>90152</t>
+          <t>89856</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>181488</t>
+          <t>180899</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>188947</t>
+          <t>188945</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>748</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>6853</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>5717</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8766</t>
+          <t>9355</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43605</t>
+          <t>43228</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51042</t>
+          <t>50782</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56456</t>
+          <t>57511</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>103861</t>
+          <t>103454</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113570</t>
+          <t>113466</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8256</t>
+          <t>8633</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>6342</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2248</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11853</t>
+          <t>12260</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>206892</t>
+          <t>207227</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>215946</t>
+          <t>216091</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>198947</t>
+          <t>198907</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>211774</t>
+          <t>211478</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>408986</t>
+          <t>409570</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>425690</t>
+          <t>425520</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2879</t>
+          <t>2734</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11933</t>
+          <t>11598</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6794</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19325</t>
+          <t>19365</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11407</t>
+          <t>11577</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28111</t>
+          <t>27527</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>100324</t>
+          <t>100826</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>111590</t>
+          <t>111604</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>137272</t>
+          <t>136492</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>152432</t>
+          <t>152293</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>242216</t>
+          <t>242452</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>261141</t>
+          <t>260557</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,38%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>7824</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19104</t>
+          <t>18602</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10185</t>
+          <t>10324</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25345</t>
+          <t>26125</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20904</t>
+          <t>21488</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39829</t>
+          <t>39593</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>58684</t>
+          <t>58853</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66331</t>
+          <t>66649</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>60540</t>
+          <t>60407</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69668</t>
+          <t>69627</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>122501</t>
+          <t>121650</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>134784</t>
+          <t>134472</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>10042</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11463</t>
+          <t>11596</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>6426</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18397</t>
+          <t>19248</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,66%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>616814</t>
+          <t>616128</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>635374</t>
+          <t>634767</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,82 +10711,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>93,61%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>96,45%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>709422</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>696483</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>719961</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>94,69%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>92,96%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>96,09%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1788</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1335941</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>1318983</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>1349203</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>94,92%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>93,72%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>96,54%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>709422</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>696560</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>719678</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>94,69%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>92,97%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>96,06%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1788</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1335941</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>1319988</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>1350052</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>94,92%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>93,79%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,87%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22779</t>
+          <t>23386</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41339</t>
+          <t>42025</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,82 +10824,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>6,39%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>39803</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>29264</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>52742</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>5,31%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>3,91%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>71437</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>58175</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>88395</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>5,08%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>6,28%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>39803</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>29547</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>52665</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>5,31%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>3,94%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>7,03%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>71437</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>57326</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>87390</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>5,08%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>6,21%</t>
         </is>
       </c>
     </row>
